--- a/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
+++ b/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -515,7 +515,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -597,7 +597,7 @@
     <t>DeviceUseStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|Procedure|Claim|Observation|QuestionnaireResponse|DocumentReference)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1|Procedure|4.0.1|Claim|4.0.1|Observation|4.0.1|QuestionnaireResponse|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -711,7 +711,7 @@
     <t>DeviceUseStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference|Media)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1|Media|4.0.1)
 </t>
   </si>
   <si>
@@ -748,7 +748,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -810,7 +810,7 @@
     <t>DeviceUseStatement.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>78</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>87</v>

--- a/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
+++ b/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
+++ b/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
+++ b/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
+++ b/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
+++ b/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
+++ b/fhir/StructureDefinition-ehealth-deviceusestatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
